--- a/Weekly_Performance_Report_JP.xlsx
+++ b/Weekly_Performance_Report_JP.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="24">
   <si>
     <t>文件名称</t>
   </si>
@@ -42,16 +42,22 @@
     <t>寄样总支出(含物流)</t>
   </si>
   <si>
-    <t>All order-2026-01-19-04_50.csv</t>
-  </si>
-  <si>
-    <t>All order-2026-01-12-03_05.csv</t>
-  </si>
-  <si>
-    <t>2026-01-18</t>
-  </si>
-  <si>
-    <t>2026-01-11</t>
+    <t>All order-2026-01-21-18_41.csv</t>
+  </si>
+  <si>
+    <t>All order-2026-01-21-18_42.csv</t>
+  </si>
+  <si>
+    <t>All order-2026-01-22-18_49.csv</t>
+  </si>
+  <si>
+    <t>2026-01-21</t>
+  </si>
+  <si>
+    <t>2026-01-20</t>
+  </si>
+  <si>
+    <t>2026-01-22</t>
   </si>
   <si>
     <t>日期</t>
@@ -76,9 +82,6 @@
   </si>
   <si>
     <t>电动剃眉刀</t>
-  </si>
-  <si>
-    <t>白色睫毛推</t>
   </si>
   <si>
     <t>车载手机支架</t>
@@ -442,7 +445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -476,25 +479,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2">
-        <v>70810</v>
+        <v>5400</v>
       </c>
       <c r="D2">
-        <v>3540.5</v>
+        <v>270</v>
       </c>
       <c r="E2">
-        <v>69844</v>
+        <v>5340</v>
       </c>
       <c r="F2">
-        <v>298.4</v>
+        <v>23</v>
       </c>
       <c r="G2">
-        <v>922.4</v>
+        <v>62.5</v>
       </c>
       <c r="H2">
-        <v>247.3</v>
+        <v>39.2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -502,25 +505,51 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3">
-        <v>33534</v>
+        <v>3190</v>
       </c>
       <c r="D3">
-        <v>1676.7</v>
+        <v>159.5</v>
       </c>
       <c r="E3">
-        <v>32337</v>
+        <v>3190</v>
       </c>
       <c r="F3">
-        <v>151.8</v>
+        <v>13.8</v>
       </c>
       <c r="G3">
-        <v>412.5</v>
+        <v>42.5</v>
       </c>
       <c r="H3">
-        <v>119.7</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4">
+        <v>2060</v>
+      </c>
+      <c r="D4">
+        <v>103</v>
+      </c>
+      <c r="E4">
+        <v>2060</v>
+      </c>
+      <c r="F4">
+        <v>4.6</v>
+      </c>
+      <c r="G4">
+        <v>17.5</v>
+      </c>
+      <c r="H4">
+        <v>39.2</v>
       </c>
     </row>
   </sheetData>
@@ -530,137 +559,189 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C2">
-        <v>33534</v>
+        <v>2160</v>
       </c>
       <c r="D2">
-        <v>1676.7</v>
+        <v>108</v>
       </c>
       <c r="E2">
-        <v>32337</v>
+        <v>2160</v>
       </c>
       <c r="F2">
-        <v>151.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G2">
-        <v>412.5</v>
+        <v>25</v>
       </c>
       <c r="H2">
-        <v>119.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C3">
-        <v>41040</v>
+        <v>1030</v>
       </c>
       <c r="D3">
-        <v>2052</v>
+        <v>51.5</v>
       </c>
       <c r="E3">
-        <v>40074</v>
+        <v>1030</v>
       </c>
       <c r="F3">
-        <v>174.8</v>
+        <v>4.6</v>
       </c>
       <c r="G3">
-        <v>475</v>
+        <v>17.5</v>
       </c>
       <c r="H3">
-        <v>136.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4">
-        <v>1960</v>
+        <v>5400</v>
       </c>
       <c r="D4">
-        <v>98</v>
+        <v>270</v>
       </c>
       <c r="E4">
-        <v>1960</v>
+        <v>5340</v>
       </c>
       <c r="F4">
-        <v>17.8</v>
+        <v>23</v>
       </c>
       <c r="G4">
-        <v>44.9</v>
+        <v>62.5</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>22.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
         <v>21</v>
       </c>
-      <c r="C5">
-        <v>27810</v>
-      </c>
-      <c r="D5">
-        <v>1390.5</v>
-      </c>
-      <c r="E5">
-        <v>27810</v>
-      </c>
-      <c r="F5">
-        <v>105.8</v>
-      </c>
-      <c r="G5">
-        <v>402.5</v>
-      </c>
-      <c r="H5">
-        <v>110.5</v>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>17.1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7">
+        <v>2060</v>
+      </c>
+      <c r="D7">
+        <v>103</v>
+      </c>
+      <c r="E7">
+        <v>2060</v>
+      </c>
+      <c r="F7">
+        <v>4.6</v>
+      </c>
+      <c r="G7">
+        <v>17.5</v>
+      </c>
+      <c r="H7">
+        <v>22.1</v>
       </c>
     </row>
   </sheetData>
@@ -670,51 +751,49 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2">
-        <v>38</v>
-      </c>
-      <c r="C2">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="B3">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
